--- a/data/trans_orig/P55S_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P55S_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26515</t>
+          <t>27101</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28245</t>
+          <t>29034</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>39057</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36159</t>
+          <t>36236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50812</t>
+          <t>51309</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69056</t>
+          <t>69339</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86626</t>
+          <t>86833</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11199</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>22566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44427</t>
+          <t>43984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>33515</t>
+          <t>32057</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>59024</t>
+          <t>57578</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61935</t>
+          <t>62271</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75363</t>
+          <t>75594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100064</t>
+          <t>99710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124341</t>
+          <t>125468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166514</t>
+          <t>167756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196622</t>
+          <t>196142</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7770</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20082</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22788</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37231</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61369</t>
+          <t>61772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>50924</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>78033</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93830</t>
+          <t>95517</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111202</t>
+          <t>112116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>142671</t>
+          <t>143405</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170169</t>
+          <t>171563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242664</t>
+          <t>243818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276184</t>
+          <t>276047</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>31372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41664</t>
+          <t>41582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2911,12 +2911,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46371</t>
+          <t>45497</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60543</t>
+          <t>60445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82339</t>
+          <t>81333</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>99414</t>
+          <t>99212</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25758</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24588</t>
+          <t>25810</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50029</t>
+          <t>49358</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41954</t>
+          <t>40458</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67754</t>
+          <t>69970</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>17271</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34962</t>
+          <t>34679</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59708</t>
+          <t>59758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42727</t>
+          <t>44278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70706</t>
+          <t>71416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60403</t>
+          <t>60956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79988</t>
+          <t>80651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108692</t>
+          <t>108171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139283</t>
+          <t>139180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>178242</t>
+          <t>175426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212667</t>
+          <t>210770</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31659</t>
+          <t>30850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57212</t>
+          <t>55298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49057</t>
+          <t>46865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79054</t>
+          <t>77622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21947</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40282</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67456</t>
+          <t>67903</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50726</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>81041</t>
+          <t>81677</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95066</t>
+          <t>94950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118364</t>
+          <t>117915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160443</t>
+          <t>161679</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>194581</t>
+          <t>194899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>264910</t>
+          <t>264053</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>304739</t>
+          <t>302962</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13353</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4627,42 +4627,42 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13594</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7399</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21690</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>16,55%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13594</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7982</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21115</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22521</t>
+          <t>23261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -4833,12 +4833,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23308</t>
+          <t>23316</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30377</t>
+          <t>30393</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44717</t>
+          <t>45453</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62039</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72982</t>
+          <t>73323</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92351</t>
+          <t>91975</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,05%</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>18578</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24194</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43679</t>
+          <t>42470</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>33945</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>59489</t>
+          <t>59804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>10588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29012</t>
+          <t>28334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>35726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -5402,12 +5402,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58962</t>
+          <t>58929</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73856</t>
+          <t>74294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5417,12 +5417,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113363</t>
+          <t>111206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140811</t>
+          <t>141150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>177530</t>
+          <t>176971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209268</t>
+          <t>209893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,23%</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>21342</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5600,12 +5600,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>30741</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59190</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>46327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75345</t>
+          <t>76812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33425</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39917</t>
+          <t>40914</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -5971,12 +5971,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85574</t>
+          <t>86182</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102806</t>
+          <t>102965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>161820</t>
+          <t>163000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196479</t>
+          <t>197302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>256971</t>
+          <t>256240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294292</t>
+          <t>293586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6169,12 +6169,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -6539,32 +6539,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6574,32 +6574,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6609,32 +6609,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>22151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -6652,32 +6652,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6687,32 +6687,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>18123</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6722,32 +6722,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>22628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -6765,32 +6765,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>33134</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40657</t>
+          <t>44569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51275</t>
+          <t>56229</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45102</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56423</t>
+          <t>62116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6835,32 +6835,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>87245</t>
+          <t>95829</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79306</t>
+          <t>87991</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94542</t>
+          <t>103637</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -6878,32 +6878,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6948,32 +6948,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -6991,17 +6991,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>50416</t>
+          <t>55062</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50416</t>
+          <t>55062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50416</t>
+          <t>55062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7026,17 +7026,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>73031</t>
+          <t>80518</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73031</t>
+          <t>80518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73031</t>
+          <t>80518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7061,17 +7061,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>123447</t>
+          <t>135580</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>123447</t>
+          <t>135580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123447</t>
+          <t>135580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7108,32 +7108,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>20009</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7143,32 +7143,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38886</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30967</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48182</t>
+          <t>53538</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7178,32 +7178,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>52438</t>
+          <t>57185</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43057</t>
+          <t>45779</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>63407</t>
+          <t>68922</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -7221,32 +7221,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26935</t>
+          <t>29021</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34515</t>
+          <t>37601</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7256,32 +7256,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>71858</t>
+          <t>76203</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63032</t>
+          <t>65064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82833</t>
+          <t>87507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7291,32 +7291,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>98793</t>
+          <t>105224</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87750</t>
+          <t>92811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110830</t>
+          <t>118861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -7334,32 +7334,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61390</t>
+          <t>65791</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53666</t>
+          <t>57429</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69643</t>
+          <t>73736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133442</t>
+          <t>145028</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122768</t>
+          <t>132698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145085</t>
+          <t>158974</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>194831</t>
+          <t>210818</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180325</t>
+          <t>195108</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>208128</t>
+          <t>225556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -7447,22 +7447,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7482,32 +7482,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>17554</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22437</t>
+          <t>24377</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -7560,17 +7560,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>106657</t>
+          <t>114059</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106657</t>
+          <t>114059</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106657</t>
+          <t>114059</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7595,17 +7595,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>255217</t>
+          <t>276723</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>255217</t>
+          <t>276723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>255217</t>
+          <t>276723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>361873</t>
+          <t>390782</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>361873</t>
+          <t>390782</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361873</t>
+          <t>390782</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7677,32 +7677,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27537</t>
+          <t>29611</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>46719</t>
+          <t>51453</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56963</t>
+          <t>63046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>67127</t>
+          <t>73016</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56792</t>
+          <t>61699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78408</t>
+          <t>86615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -7790,32 +7790,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23987</t>
+          <t>25514</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39990</t>
+          <t>42969</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7825,32 +7825,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82087</t>
+          <t>88200</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70747</t>
+          <t>77410</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93233</t>
+          <t>99502</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>112993</t>
+          <t>121282</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>99982</t>
+          <t>107829</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>127441</t>
+          <t>136101</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -7903,32 +7903,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>97360</t>
+          <t>105391</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86949</t>
+          <t>94890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106047</t>
+          <t>116083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7938,32 +7938,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>184717</t>
+          <t>201256</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173191</t>
+          <t>188291</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199055</t>
+          <t>213580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7973,32 +7973,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>282077</t>
+          <t>306647</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>265981</t>
+          <t>288067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298555</t>
+          <t>322803</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -8016,32 +8016,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8051,32 +8051,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8086,32 +8086,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>34345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -8129,17 +8129,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>157073</t>
+          <t>169121</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>157073</t>
+          <t>169121</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>157073</t>
+          <t>169121</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8164,17 +8164,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>328248</t>
+          <t>357241</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>328248</t>
+          <t>357241</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>328248</t>
+          <t>357241</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8199,17 +8199,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>485321</t>
+          <t>526362</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>485321</t>
+          <t>526362</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>485321</t>
+          <t>526362</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
